--- a/Data/FlightPlan/FPL_02OCT26.xlsx
+++ b/Data/FlightPlan/FPL_02OCT26.xlsx
@@ -356,7 +356,7 @@
     <t>18:20</t>
   </si>
   <si>
-    <t>19:08</t>
+    <t>19:27</t>
   </si>
   <si>
     <t>18:50</t>
@@ -608,987 +608,1017 @@
     <t>20:30</t>
   </si>
   <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:41</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>15:51</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>18:31</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>09:29</t>
+  </si>
+  <si>
+    <t>11:59</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:59</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>19:49</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>16:28</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
     <t>20:00</t>
   </si>
   <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>21:00</t>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:52</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>14:28</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>12:26</t>
+  </si>
+  <si>
+    <t>18:13</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:17</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>15:43</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:53</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>21:12</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:00</t>
   </si>
   <si>
     <t>22:25</t>
   </si>
   <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:39</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:41</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>15:51</t>
-  </si>
-  <si>
-    <t>17:10</t>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:53</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>14:58</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>20:14</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>06:58</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>15:31</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>11:39</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:27</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>15:09</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>10:33</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>17:01</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>13:33</t>
+  </si>
+  <si>
+    <t>16:31</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>18:03</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>TSN</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>09:18</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>16:22</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>13:06</t>
+  </si>
+  <si>
+    <t>DYG</t>
+  </si>
+  <si>
+    <t>20:47</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>07:49</t>
+  </si>
+  <si>
+    <t>10:28</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:09</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>09:59</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>08:12</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>17:32</t>
+  </si>
+  <si>
+    <t>19:38</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>11:03</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>16:33</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>14:36</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>20:43</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>09:17</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:41</t>
+  </si>
+  <si>
+    <t>08:28</t>
+  </si>
+  <si>
+    <t>13:13</t>
+  </si>
+  <si>
+    <t>18:56</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>09:06</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>17:37</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>16:26</t>
+  </si>
+  <si>
+    <t>18:37</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>17:16</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
+  </si>
+  <si>
+    <t>20:33</t>
+  </si>
+  <si>
+    <t>VN-A697</t>
+  </si>
+  <si>
+    <t>06:42</t>
+  </si>
+  <si>
+    <t>19:24</t>
+  </si>
+  <si>
+    <t>VN-A698</t>
+  </si>
+  <si>
+    <t>09:02</t>
   </si>
   <si>
     <t>18:26</t>
   </si>
   <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>09:29</t>
-  </si>
-  <si>
-    <t>11:59</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:59</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:28</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:37</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:52</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>14:28</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:44</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>18:13</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:17</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>15:43</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>21:12</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>18:31</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:53</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:28</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:58</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>20:14</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>12:29</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>06:58</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>15:31</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>11:39</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:27</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>15:09</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:16</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:07</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>10:33</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>13:49</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>17:01</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>13:33</t>
-  </si>
-  <si>
-    <t>16:31</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:46</t>
-  </si>
-  <si>
-    <t>18:03</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>TSN</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>09:18</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>16:22</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>13:06</t>
-  </si>
-  <si>
-    <t>DYG</t>
-  </si>
-  <si>
-    <t>20:47</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>07:49</t>
-  </si>
-  <si>
-    <t>10:28</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:09</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>03:20</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>13:32</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>18:29</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>09:59</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>08:12</t>
-  </si>
-  <si>
-    <t>10:04</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>14:23</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>17:32</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>09:03</t>
-  </si>
-  <si>
-    <t>11:03</t>
-  </si>
-  <si>
-    <t>13:54</t>
-  </si>
-  <si>
-    <t>16:33</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>08:01</t>
-  </si>
-  <si>
-    <t>10:32</t>
-  </si>
-  <si>
-    <t>12:01</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>18:17</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>09:17</t>
-  </si>
-  <si>
-    <t>12:09</t>
-  </si>
-  <si>
-    <t>15:13</t>
-  </si>
-  <si>
-    <t>03:30</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:41</t>
-  </si>
-  <si>
-    <t>08:28</t>
-  </si>
-  <si>
-    <t>13:13</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>09:06</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>15:04</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>15:07</t>
-  </si>
-  <si>
-    <t>17:37</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>08:34</t>
-  </si>
-  <si>
-    <t>13:53</t>
-  </si>
-  <si>
-    <t>16:26</t>
-  </si>
-  <si>
-    <t>18:37</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>17:16</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>12:42</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>20:33</t>
-  </si>
-  <si>
-    <t>VN-A697</t>
-  </si>
-  <si>
-    <t>06:42</t>
-  </si>
-  <si>
-    <t>VN-A698</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1598,6 +1628,9 @@
     <t>15:49</t>
   </si>
   <si>
+    <t>19:29</t>
+  </si>
+  <si>
     <t>VN-A810</t>
   </si>
   <si>
@@ -1652,13 +1685,10 @@
     <t>BNE</t>
   </si>
   <si>
-    <t>23:30</t>
-  </si>
-  <si>
     <t>Total Record(s): 372</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 02, 2026 17:31</t>
+    <t xml:space="preserve">Generated on  Oct 02, 2026 17:55</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4644,11 +4674,11 @@
         <v>198</v>
       </c>
       <c t="s" r="K84" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4675,17 +4705,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>178</v>
       </c>
       <c t="s" r="K85" s="7">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>137</v>
+        <v>201</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4715,29 +4745,29 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
+        <v>202</v>
+      </c>
+      <c r="F87" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G87" s="8">
         <v>203</v>
-      </c>
-      <c r="F87" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G87" s="8">
-        <v>204</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I87" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J87" s="7">
         <v>205</v>
       </c>
-      <c t="s" r="J87" s="7">
+      <c t="s" r="K87" s="7">
         <v>206</v>
-      </c>
-      <c t="s" r="K87" s="7">
-        <v>207</v>
       </c>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4752,7 +4782,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4764,15 +4794,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I88" s="7">
+        <v>208</v>
+      </c>
+      <c t="s" r="J88" s="7">
         <v>209</v>
-      </c>
-      <c t="s" r="J88" s="7">
-        <v>210</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4787,7 +4817,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4799,7 +4829,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>78</v>
@@ -4807,7 +4837,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4822,7 +4852,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4834,7 +4864,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>94</v>
@@ -4855,7 +4885,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4867,7 +4897,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>149</v>
@@ -4888,7 +4918,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4897,7 +4927,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="I92" s="7">
         <v>32</v>
@@ -4936,7 +4966,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4971,7 +5001,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4991,7 +5021,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -5006,7 +5036,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5018,15 +5048,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5041,7 +5071,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5050,20 +5080,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H97" s="8">
+        <v>220</v>
+      </c>
+      <c t="s" r="I97" s="7">
         <v>221</v>
-      </c>
-      <c t="s" r="I97" s="7">
-        <v>222</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>122</v>
       </c>
       <c t="s" r="K97" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>148</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5078,13 +5108,13 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>16</v>
@@ -5093,14 +5123,14 @@
         <v>148</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c t="s" r="K98" s="7">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>123</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5115,7 +5145,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5132,9 +5162,13 @@
       <c t="s" r="J99" s="7">
         <v>226</v>
       </c>
-      <c r="K99" s="7"/>
+      <c t="s" r="K99" s="7">
+        <v>178</v>
+      </c>
       <c r="L99" s="7"/>
-      <c r="M99" s="7"/>
+      <c t="s" r="M99" s="7">
+        <v>227</v>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c t="s" r="A100" s="6">
@@ -5148,7 +5182,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5160,14 +5194,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>228</v>
-      </c>
-      <c r="K100" s="7"/>
+        <v>229</v>
+      </c>
+      <c t="s" r="K100" s="7">
+        <v>230</v>
+      </c>
       <c r="L100" s="7"/>
-      <c r="M100" s="7"/>
+      <c t="s" r="M100" s="7">
+        <v>231</v>
+      </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="6"/>
@@ -5196,7 +5234,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5208,7 +5246,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>57</v>
@@ -5216,7 +5254,7 @@
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5231,7 +5269,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5251,7 +5289,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5266,7 +5304,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5278,7 +5316,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>121</v>
@@ -5286,7 +5324,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5301,7 +5339,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5313,14 +5351,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>174</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
+      <c t="s" r="M105" s="7">
+        <v>239</v>
+      </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c t="s" r="A106" s="6">
@@ -5334,7 +5374,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5343,20 +5383,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="K106" s="7">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5371,29 +5411,29 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="K107" s="7">
-        <v>242</v>
+        <v>97</v>
       </c>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>150</v>
+        <v>246</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5423,13 +5463,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
@@ -5438,7 +5478,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5458,7 +5498,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5473,12 +5513,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5493,7 +5533,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5505,10 +5545,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5526,7 +5566,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5535,13 +5575,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5574,7 +5614,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5586,7 +5626,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>101</v>
@@ -5609,7 +5649,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5629,7 +5669,7 @@
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5644,7 +5684,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5656,17 +5696,17 @@
         <v>24</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="K116" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5681,7 +5721,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5696,14 +5736,14 @@
         <v>19</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="K117" s="7">
         <v>129</v>
       </c>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5718,7 +5758,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5730,10 +5770,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="K118" s="7">
         <v>164</v>
@@ -5755,7 +5795,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5792,7 +5832,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5801,7 +5841,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="I120" s="7">
         <v>40</v>
@@ -5810,7 +5850,7 @@
         <v>178</v>
       </c>
       <c t="s" r="K120" s="7">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
@@ -5829,29 +5869,29 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="K121" s="7">
         <v>83</v>
       </c>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5881,7 +5921,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5901,7 +5941,7 @@
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5916,7 +5956,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5925,18 +5965,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="I124" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5951,26 +5991,28 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
+      <c t="s" r="M125" s="7">
+        <v>222</v>
+      </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="6"/>
@@ -5999,7 +6041,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6011,7 +6053,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>181</v>
@@ -6019,7 +6061,7 @@
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -6034,7 +6076,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6046,10 +6088,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -6067,7 +6109,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6079,7 +6121,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>136</v>
@@ -6115,27 +6157,27 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6150,7 +6192,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6170,7 +6212,7 @@
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6185,7 +6227,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6220,7 +6262,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6240,7 +6282,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6255,7 +6297,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6270,7 +6312,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6288,7 +6330,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6321,7 +6363,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6333,7 +6375,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>56</v>
@@ -6369,13 +6411,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>17</v>
@@ -6384,7 +6426,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6404,7 +6446,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6416,15 +6458,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6439,7 +6481,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6472,7 +6514,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6490,11 +6532,11 @@
         <v>177</v>
       </c>
       <c t="s" r="K142" s="7">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>200</v>
+        <v>294</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6509,7 +6551,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6521,17 +6563,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>290</v>
+        <v>243</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6561,7 +6603,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6570,10 +6612,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>160</v>
@@ -6581,7 +6623,7 @@
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6596,13 +6638,13 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>17</v>
@@ -6616,7 +6658,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6631,7 +6673,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6640,13 +6682,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6666,13 +6708,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>17</v>
@@ -6685,7 +6727,9 @@
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
+      <c t="s" r="M148" s="7">
+        <v>302</v>
+      </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c t="s" r="A149" s="6">
@@ -6699,7 +6743,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6732,7 +6776,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6744,7 +6788,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>156</v>
@@ -6780,7 +6824,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6795,12 +6839,12 @@
         <v>170</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6815,7 +6859,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6835,7 +6879,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6850,7 +6894,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6862,7 +6906,7 @@
         <v>140</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>103</v>
@@ -6898,7 +6942,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6910,7 +6954,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>171</v>
@@ -6933,7 +6977,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6955,7 +6999,7 @@
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6970,7 +7014,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6982,17 +7026,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c t="s" r="K158" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>305</v>
+        <v>219</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7007,7 +7051,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7022,14 +7066,14 @@
         <v>194</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="K159" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7044,7 +7088,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7056,17 +7100,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c t="s" r="K160" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>202</v>
+        <v>314</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7081,7 +7125,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7093,7 +7137,7 @@
         <v>140</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>170</v>
@@ -7129,7 +7173,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7141,7 +7185,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>75</v>
@@ -7149,7 +7193,7 @@
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7164,7 +7208,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7176,15 +7220,15 @@
         <v>91</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7199,7 +7243,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7214,12 +7258,12 @@
         <v>171</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7234,7 +7278,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7243,18 +7287,18 @@
         <v>119</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7269,13 +7313,13 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>119</v>
@@ -7284,7 +7328,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7302,7 +7346,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7314,10 +7358,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7350,7 +7394,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7383,7 +7427,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7392,13 +7436,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7416,22 +7460,22 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7464,7 +7508,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7479,7 +7523,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7499,7 +7543,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7511,7 +7555,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>191</v>
@@ -7519,7 +7563,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7534,7 +7578,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7543,13 +7587,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7569,13 +7613,13 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>16</v>
@@ -7604,7 +7648,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7619,14 +7663,14 @@
         <v>92</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7656,7 +7700,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7668,15 +7712,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7691,7 +7735,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7703,15 +7747,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>335</v>
+        <v>246</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7726,7 +7770,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7735,10 +7779,10 @@
         <v>59</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>61</v>
@@ -7761,19 +7805,19 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>110</v>
@@ -7796,7 +7840,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7811,12 +7855,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7831,7 +7875,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7881,7 +7925,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7893,10 +7937,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7916,7 +7960,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7931,7 +7975,7 @@
         <v>180</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7966,7 +8010,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7975,18 +8019,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8001,13 +8045,13 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>17</v>
@@ -8021,7 +8065,7 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8036,7 +8080,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8048,7 +8092,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>22</v>
@@ -8071,7 +8115,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8083,7 +8127,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>88</v>
@@ -8106,7 +8150,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8115,18 +8159,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8141,19 +8185,19 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>70</v>
@@ -8174,7 +8218,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8186,10 +8230,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -8222,7 +8266,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8237,12 +8281,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8257,7 +8301,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8275,7 +8319,7 @@
         <v>143</v>
       </c>
       <c t="s" r="K199" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
@@ -8294,7 +8338,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8309,7 +8353,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="K200" s="7">
         <v>144</v>
@@ -8331,7 +8375,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8340,17 +8384,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>183</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
-      <c r="M201" s="7"/>
+      <c t="s" r="M201" s="7">
+        <v>357</v>
+      </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c t="s" r="A202" s="6">
@@ -8364,19 +8410,19 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>95</v>
@@ -8397,7 +8443,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8409,7 +8455,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>84</v>
@@ -8445,7 +8491,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8457,7 +8503,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>187</v>
@@ -8480,7 +8526,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8515,7 +8561,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8524,13 +8570,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="I207" s="7">
         <v>189</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8550,19 +8596,19 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>191</v>
@@ -8570,7 +8616,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8585,7 +8631,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8597,7 +8643,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>35</v>
@@ -8605,7 +8651,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8635,7 +8681,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8644,18 +8690,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>150</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8670,13 +8716,13 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>16</v>
@@ -8685,12 +8731,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8705,7 +8751,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8725,7 +8771,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8740,7 +8786,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8755,7 +8801,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8775,7 +8821,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8787,17 +8833,17 @@
         <v>155</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c t="s" r="K215" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8812,7 +8858,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8827,14 +8873,14 @@
         <v>114</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>198</v>
+        <v>168</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8849,7 +8895,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8864,11 +8910,15 @@
         <v>41</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>364</v>
-      </c>
-      <c r="K217" s="7"/>
+        <v>370</v>
+      </c>
+      <c t="s" r="K217" s="7">
+        <v>313</v>
+      </c>
       <c r="L217" s="7"/>
-      <c r="M217" s="7"/>
+      <c t="s" r="M217" s="7">
+        <v>371</v>
+      </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c r="A218" s="6"/>
@@ -8897,7 +8947,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8912,7 +8962,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8932,7 +8982,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8944,15 +8994,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8967,7 +9017,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8982,12 +9032,12 @@
         <v>163</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9002,7 +9052,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9037,7 +9087,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9049,10 +9099,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -9085,7 +9135,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9097,15 +9147,15 @@
         <v>59</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9120,7 +9170,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9140,7 +9190,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9155,7 +9205,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9170,7 +9220,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9190,7 +9240,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9205,14 +9255,14 @@
         <v>65</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="K228" s="7">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9227,7 +9277,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9239,17 +9289,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>39</v>
       </c>
       <c t="s" r="K229" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9279,7 +9329,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9299,7 +9349,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9314,7 +9364,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9326,7 +9376,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>22</v>
@@ -9334,7 +9384,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9349,7 +9399,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9386,7 +9436,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9438,7 +9488,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9447,7 +9497,7 @@
         <v>59</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>153</v>
@@ -9458,7 +9508,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9473,19 +9523,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>59</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>145</v>
@@ -9493,7 +9543,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9523,7 +9573,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9535,15 +9585,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9558,7 +9608,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9567,7 +9617,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="I240" s="7">
         <v>34</v>
@@ -9578,7 +9628,7 @@
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9593,13 +9643,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
@@ -9613,7 +9663,7 @@
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9628,7 +9678,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9643,14 +9693,14 @@
         <v>29</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c t="s" r="K242" s="7">
         <v>29</v>
       </c>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9665,7 +9715,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9677,17 +9727,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="K243" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9702,7 +9752,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9714,7 +9764,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>239</v>
+        <v>392</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>100</v>
@@ -9750,7 +9800,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9762,15 +9812,15 @@
         <v>91</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9785,7 +9835,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9797,15 +9847,15 @@
         <v>186</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9820,7 +9870,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9853,7 +9903,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9865,7 +9915,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>138</v>
@@ -9901,27 +9951,27 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9936,7 +9986,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9948,17 +9998,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="K252" s="7">
         <v>40</v>
       </c>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9973,7 +10023,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9988,7 +10038,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>394</v>
+        <v>199</v>
       </c>
       <c t="s" r="K253" s="7">
         <v>71</v>
@@ -10010,7 +10060,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10019,13 +10069,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -10054,17 +10104,17 @@
         <v>22</v>
       </c>
       <c t="s" r="C256" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>17</v>
@@ -10073,7 +10123,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>398</v>
+        <v>227</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -10106,7 +10156,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10115,13 +10165,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c t="s" r="I258" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -10141,22 +10191,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -10176,7 +10226,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10194,7 +10244,7 @@
         <v>191</v>
       </c>
       <c t="s" r="K260" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
@@ -10213,7 +10263,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10228,14 +10278,14 @@
         <v>130</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c t="s" r="K261" s="7">
         <v>29</v>
       </c>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>272</v>
+        <v>410</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10250,7 +10300,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10268,11 +10318,11 @@
         <v>29</v>
       </c>
       <c t="s" r="K262" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10287,7 +10337,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10302,7 +10352,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="K263" s="7">
         <v>136</v>
@@ -10339,7 +10389,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10351,15 +10401,15 @@
         <v>186</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10374,7 +10424,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10386,7 +10436,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>335</v>
+        <v>246</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>98</v>
@@ -10394,7 +10444,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10409,7 +10459,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10424,12 +10474,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10444,7 +10494,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10456,7 +10506,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>172</v>
@@ -10464,7 +10514,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10479,7 +10529,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10494,12 +10544,12 @@
         <v>133</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10514,7 +10564,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10526,10 +10576,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10547,7 +10597,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10559,14 +10609,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>276</v>
-      </c>
-      <c r="K271" s="7"/>
+        <v>281</v>
+      </c>
+      <c t="s" r="K271" s="7">
+        <v>94</v>
+      </c>
       <c r="L271" s="7"/>
-      <c r="M271" s="7"/>
+      <c t="s" r="M271" s="7">
+        <v>199</v>
+      </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
       <c t="s" r="A272" s="6">
@@ -10580,7 +10634,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10628,7 +10682,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -10637,10 +10691,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>128</v>
@@ -10648,7 +10702,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10663,13 +10717,13 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>16</v>
@@ -10683,7 +10737,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10698,7 +10752,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10707,10 +10761,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>198</v>
@@ -10718,7 +10772,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10733,22 +10787,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10781,7 +10835,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10790,10 +10844,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>102</v>
@@ -10801,7 +10855,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10816,19 +10870,19 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>104</v>
@@ -10836,7 +10890,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10851,7 +10905,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10860,10 +10914,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>64</v>
@@ -10871,7 +10925,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10886,13 +10940,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>17</v>
@@ -10906,7 +10960,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10921,7 +10975,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10941,7 +10995,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10956,7 +11010,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10968,10 +11022,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10989,7 +11043,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11004,11 +11058,15 @@
         <v>168</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>240</v>
-      </c>
-      <c r="K285" s="7"/>
+        <v>244</v>
+      </c>
+      <c t="s" r="K285" s="7">
+        <v>136</v>
+      </c>
       <c r="L285" s="7"/>
-      <c r="M285" s="7"/>
+      <c t="s" r="M285" s="7">
+        <v>330</v>
+      </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
       <c r="A286" s="6"/>
@@ -11037,7 +11095,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11049,7 +11107,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>84</v>
@@ -11057,7 +11115,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11072,7 +11130,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11084,15 +11142,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11107,7 +11165,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11119,7 +11177,7 @@
         <v>196</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>110</v>
@@ -11127,7 +11185,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11142,7 +11200,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11154,7 +11212,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>26</v>
@@ -11177,7 +11235,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11186,7 +11244,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>89</v>
@@ -11195,11 +11253,11 @@
         <v>97</v>
       </c>
       <c t="s" r="K291" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11214,29 +11272,29 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c t="s" r="K292" s="7">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11266,7 +11324,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11275,18 +11333,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11301,27 +11359,27 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11336,7 +11394,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11351,12 +11409,12 @@
         <v>133</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11371,7 +11429,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11383,7 +11441,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>135</v>
@@ -11391,7 +11449,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>433</v>
+        <v>219</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11406,7 +11464,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11415,7 +11473,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>92</v>
@@ -11428,7 +11486,7 @@
       </c>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11443,13 +11501,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>16</v>
@@ -11458,7 +11516,7 @@
         <v>176</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c t="s" r="K299" s="7">
         <v>41</v>
@@ -11480,7 +11538,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11492,14 +11550,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>30</v>
       </c>
-      <c r="K300" s="7"/>
+      <c t="s" r="K300" s="7">
+        <v>442</v>
+      </c>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>32</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c r="A301" s="6"/>
@@ -11528,7 +11590,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11537,10 +11599,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>102</v>
@@ -11548,7 +11610,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11563,27 +11625,27 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11598,7 +11660,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11607,7 +11669,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>50</v>
@@ -11616,11 +11678,11 @@
         <v>22</v>
       </c>
       <c t="s" r="K304" s="7">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11635,13 +11697,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>16</v>
@@ -11653,11 +11715,11 @@
         <v>111</v>
       </c>
       <c t="s" r="K305" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11672,7 +11734,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11681,10 +11743,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>194</v>
@@ -11692,7 +11754,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>372</v>
+        <v>336</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11707,13 +11769,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>16</v>
@@ -11722,7 +11784,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11740,7 +11802,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11755,14 +11817,14 @@
         <v>175</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c t="s" r="K308" s="7">
         <v>41</v>
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11777,7 +11839,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11789,17 +11851,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>442</v>
+        <v>201</v>
       </c>
       <c t="s" r="K309" s="7">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11829,7 +11891,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11841,15 +11903,15 @@
         <v>125</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11864,7 +11926,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11876,7 +11938,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>157</v>
@@ -11884,7 +11946,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11899,7 +11961,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11908,18 +11970,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11934,13 +11996,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>16</v>
@@ -11949,12 +12011,12 @@
         <v>107</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11969,7 +12031,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11978,7 +12040,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>171</v>
@@ -11989,7 +12051,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12004,27 +12066,27 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12039,7 +12101,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -12054,14 +12116,14 @@
         <v>76</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="K317" s="7">
         <v>146</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>330</v>
+        <v>357</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12076,7 +12138,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -12094,11 +12156,11 @@
         <v>39</v>
       </c>
       <c t="s" r="K318" s="7">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>393</v>
+        <v>199</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12128,7 +12190,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12137,10 +12199,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>182</v>
@@ -12163,13 +12225,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>17</v>
@@ -12198,7 +12260,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12218,7 +12280,7 @@
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12233,7 +12295,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -12252,7 +12314,9 @@
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
-      <c r="M323" s="7"/>
+      <c t="s" r="M323" s="7">
+        <v>463</v>
+      </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
       <c t="s" r="A324" s="6">
@@ -12266,7 +12330,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -12278,7 +12342,7 @@
         <v>224</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>30</v>
@@ -12299,7 +12363,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12311,10 +12375,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -12347,7 +12411,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12367,7 +12431,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12382,7 +12446,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12394,7 +12458,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>19</v>
@@ -12402,7 +12466,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12417,7 +12481,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12429,7 +12493,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>76</v>
@@ -12437,7 +12501,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12452,7 +12516,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12472,7 +12536,7 @@
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12487,7 +12551,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12496,7 +12560,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="I331" s="7">
         <v>39</v>
@@ -12520,22 +12584,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>394</v>
+        <v>199</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12568,7 +12632,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12577,7 +12641,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c t="s" r="I334" s="7">
         <v>18</v>
@@ -12603,13 +12667,13 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>17</v>
@@ -12638,7 +12702,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12647,13 +12711,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>466</v>
+        <v>357</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12671,22 +12735,22 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -12719,7 +12783,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12731,15 +12795,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12754,7 +12818,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12769,12 +12833,12 @@
         <v>57</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12789,7 +12853,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12801,7 +12865,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>182</v>
@@ -12809,7 +12873,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12824,7 +12888,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12844,7 +12908,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12859,7 +12923,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12894,7 +12958,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12906,7 +12970,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>168</v>
@@ -12942,7 +13006,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12954,7 +13018,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>181</v>
@@ -12977,7 +13041,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12986,18 +13050,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13012,13 +13076,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>17</v>
@@ -13027,11 +13091,13 @@
         <v>116</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
-      <c r="M348" s="7"/>
+      <c t="s" r="M348" s="7">
+        <v>484</v>
+      </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
       <c t="s" r="A349" s="6">
@@ -13045,7 +13111,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -13054,10 +13120,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>170</v>
@@ -13093,7 +13159,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13105,15 +13171,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13128,7 +13194,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13140,7 +13206,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>191</v>
@@ -13148,7 +13214,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13163,7 +13229,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13183,7 +13249,7 @@
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13198,7 +13264,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -13213,7 +13279,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -13233,7 +13299,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13242,10 +13308,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>44</v>
@@ -13255,7 +13321,7 @@
       </c>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13270,29 +13336,29 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c t="s" r="K356" s="7">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13322,7 +13388,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13331,10 +13397,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>156</v>
@@ -13342,7 +13408,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13357,13 +13423,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>16</v>
@@ -13377,7 +13443,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13392,7 +13458,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -13407,14 +13473,14 @@
         <v>103</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="K360" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13429,7 +13495,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -13441,17 +13507,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c t="s" r="K361" s="7">
         <v>21</v>
       </c>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13466,7 +13532,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -13475,10 +13541,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>164</v>
@@ -13501,26 +13567,28 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>92</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
-      <c r="M363" s="7"/>
+      <c t="s" r="M363" s="7">
+        <v>496</v>
+      </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
       <c t="s" r="A364" s="6">
@@ -13534,7 +13602,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -13543,7 +13611,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c t="s" r="I364" s="7">
         <v>39</v>
@@ -13556,7 +13624,7 @@
       </c>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13571,13 +13639,13 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>16</v>
@@ -13593,7 +13661,7 @@
       </c>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13623,7 +13691,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13638,12 +13706,12 @@
         <v>187</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>489</v>
+        <v>498</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13658,7 +13726,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -13670,15 +13738,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>491</v>
+        <v>500</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13693,7 +13761,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13708,12 +13776,12 @@
         <v>130</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>492</v>
+        <v>501</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13728,7 +13796,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13748,7 +13816,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13763,7 +13831,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13775,7 +13843,7 @@
         <v>59</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>81</v>
@@ -13796,7 +13864,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13811,7 +13879,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>493</v>
+        <v>294</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13844,7 +13912,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13856,15 +13924,15 @@
         <v>119</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>335</v>
+        <v>246</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13879,7 +13947,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13891,15 +13959,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13914,7 +13982,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13932,7 +14000,7 @@
         <v>64</v>
       </c>
       <c t="s" r="K376" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
@@ -13951,7 +14019,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13966,14 +14034,14 @@
         <v>108</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c t="s" r="K377" s="7">
         <v>143</v>
       </c>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13988,7 +14056,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -14000,17 +14068,17 @@
         <v>155</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c t="s" r="K378" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14025,7 +14093,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -14037,13 +14105,13 @@
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c t="s" r="K379" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
@@ -14077,7 +14145,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -14089,15 +14157,15 @@
         <v>24</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14112,7 +14180,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -14124,15 +14192,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14147,7 +14215,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -14159,7 +14227,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>181</v>
@@ -14167,7 +14235,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14182,7 +14250,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -14194,15 +14262,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14217,7 +14285,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -14232,12 +14300,12 @@
         <v>68</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>505</v>
+        <v>513</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14267,7 +14335,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14282,12 +14350,12 @@
         <v>187</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14302,7 +14370,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14314,7 +14382,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>135</v>
@@ -14322,7 +14390,7 @@
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14337,7 +14405,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14349,7 +14417,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>166</v>
@@ -14357,7 +14425,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>93</v>
+        <v>277</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14372,7 +14440,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14381,13 +14449,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>202</v>
+        <v>314</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -14405,22 +14473,22 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -14453,7 +14521,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -14462,18 +14530,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>141</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14488,13 +14556,13 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
@@ -14503,12 +14571,12 @@
         <v>181</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14523,7 +14591,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14532,7 +14600,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>192</v>
@@ -14543,7 +14611,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>466</v>
+        <v>357</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14558,22 +14626,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14606,7 +14674,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14615,18 +14683,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>187</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14641,13 +14709,13 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>17</v>
@@ -14676,7 +14744,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14685,18 +14753,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14711,13 +14779,13 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>17</v>
@@ -14726,7 +14794,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14759,7 +14827,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14768,10 +14836,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>161</v>
@@ -14794,22 +14862,22 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14829,7 +14897,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14838,10 +14906,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>97</v>
@@ -14866,29 +14934,29 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c t="s" r="H406" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14918,7 +14986,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14930,13 +14998,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c t="s" r="K408" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
@@ -14955,7 +15023,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14977,7 +15045,7 @@
       </c>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14992,7 +15060,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -15004,10 +15072,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -15025,7 +15093,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -15037,10 +15105,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>398</v>
+        <v>227</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -15073,7 +15141,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -15085,15 +15153,15 @@
         <v>196</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15108,7 +15176,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -15117,10 +15185,10 @@
         <v>196</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>180</v>
@@ -15143,27 +15211,27 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>196</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15178,7 +15246,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -15198,7 +15266,7 @@
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15213,7 +15281,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -15248,7 +15316,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15267,7 +15335,9 @@
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
-      <c r="M418" s="7"/>
+      <c t="s" r="M418" s="7">
+        <v>532</v>
+      </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
       <c t="s" r="A419" s="6">
@@ -15281,7 +15351,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15293,17 +15363,17 @@
         <v>59</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="K419" s="7">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15318,7 +15388,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15333,10 +15403,10 @@
         <v>41</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c t="s" r="K420" s="7">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
@@ -15370,7 +15440,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15390,7 +15460,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>525</v>
+        <v>534</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15405,7 +15475,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -15420,12 +15490,12 @@
         <v>189</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15440,7 +15510,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -15477,7 +15547,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15499,7 +15569,7 @@
       </c>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15514,7 +15584,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15534,7 +15604,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>220</v>
+        <v>535</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15549,7 +15619,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15564,7 +15634,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -15597,7 +15667,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -15609,7 +15679,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>141</v>
@@ -15617,7 +15687,7 @@
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15632,7 +15702,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -15644,15 +15714,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15667,7 +15737,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -15679,7 +15749,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>67</v>
@@ -15687,7 +15757,7 @@
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>528</v>
+        <v>538</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -15702,7 +15772,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -15722,7 +15792,7 @@
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>237</v>
+        <v>539</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15752,7 +15822,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="F434" s="7">
         <v>330</v>
@@ -15761,18 +15831,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15787,22 +15857,22 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="F435" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15835,7 +15905,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="F437" s="7">
         <v>330</v>
@@ -15844,13 +15914,13 @@
         <v>119</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15868,22 +15938,22 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="F438" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>119</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15916,7 +15986,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="F440" s="7">
         <v>330</v>
@@ -15925,18 +15995,18 @@
         <v>119</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c t="s" r="I440" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15951,19 +16021,19 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="F441" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>119</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>156</v>
@@ -16003,7 +16073,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="F443" s="7">
         <v>330</v>
@@ -16012,18 +16082,18 @@
         <v>119</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16038,13 +16108,13 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="F444" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>119</v>
@@ -16053,7 +16123,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -16086,7 +16156,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F446" s="7">
         <v>330</v>
@@ -16095,7 +16165,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c t="s" r="I446" s="7">
         <v>75</v>
@@ -16106,7 +16176,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>540</v>
+        <v>551</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16121,13 +16191,13 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F447" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>16</v>
@@ -16136,12 +16206,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>541</v>
+        <v>552</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16156,7 +16226,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F448" s="7">
         <v>330</v>
@@ -16171,7 +16241,7 @@
         <v>176</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -16189,7 +16259,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="F449" s="7">
         <v>330</v>
@@ -16201,10 +16271,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -16237,22 +16307,22 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="F451" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="K451" s="7">
         <v>129</v>
@@ -16289,7 +16359,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="F453" s="7">
         <v>330</v>
@@ -16298,13 +16368,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -16324,22 +16394,22 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>547</v>
+        <v>442</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -16347,7 +16417,7 @@
     </row>
     <row r="455" ht="16.5" customHeight="1">
       <c t="s" r="A455" s="9">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="B455" s="9"/>
       <c r="C455" s="9"/>
@@ -16367,7 +16437,7 @@
     <row r="456" ht="65.25" customHeight="1"/>
     <row r="457" ht="16.5" customHeight="1">
       <c t="s" r="A457" s="10">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B457" s="10"/>
       <c r="C457" s="10"/>
@@ -16380,7 +16450,7 @@
       <c r="J457" s="10"/>
       <c r="K457" s="10"/>
       <c t="s" r="L457" s="11">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="M457" s="11"/>
       <c r="N457" s="11"/>
